--- a/loan_free.xlsx
+++ b/loan_free.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>loan_amount</t>
   </si>
@@ -77,9 +77,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -360,12 +361,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
@@ -377,7 +378,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
@@ -394,7 +395,7 @@
       <c r="B2" s="1">
         <v>46271</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>100000</v>
       </c>
       <c r="D2" s="1">
@@ -411,17 +412,35 @@
       <c r="B3" s="1">
         <v>46210</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>100000</v>
       </c>
       <c r="D3" s="1">
-        <v>46210</v>
+        <v>46575</v>
       </c>
       <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46291</v>
+      </c>
+      <c r="C4" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46656</v>
+      </c>
+      <c r="E4" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>